--- a/output/quickfixclose2_portfolio_daily.xlsx
+++ b/output/quickfixclose2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>397,559.41</t>
+          <t>404,991.67</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+297.56%</t>
+          <t>+304.99%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>410,755  (+310.76%)</t>
+          <t>418,568  (+318.57%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,308  (13.2 pts of return)</t>
+          <t>5,441  (13.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25.0x</t>
+          <t>25.7x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+4.30R  (best +21.10R)</t>
+          <t>+4.26R  (best +21.10R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,715  (+4.30%)</t>
+          <t>7,706  (+4.26%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>54% of trading days</t>
+          <t>55% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5507,22 +5507,50 @@
         <v>46233</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>397559.41</v>
+        <v>397692.13</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>-0</v>
+        <v>3317.97</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>397559.41</v>
+        <v>394374.15</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_close (+62,913)</t>
+          <t>US_Dollar_Index_Futures exit_close (+62,913)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures exit_close (+7,300)</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10080,7 @@
         <v>126633.18</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>632332.8100000001</v>
+        <v>632610.8</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -10076,14 +10104,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="G89" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.04</v>
+        <v>2.2</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>499976.04</v>
@@ -10091,15 +10127,15 @@
       <c r="J89" s="5" t="n">
         <v>6949.67</v>
       </c>
-      <c r="K89" s="6" t="n">
-        <v>-277.99</v>
+      <c r="K89" s="7" t="n">
+        <v>15289.27</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>505699.63</v>
+        <v>647900.0600000001</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose2_portfolio_daily.xlsx
+++ b/output/quickfixclose2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>55% of trading days</t>
+          <t>54% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5553,6 +5553,46 @@
           <t>NY_Natural_Gas_Futures exit_close (+7,300)</t>
         </is>
       </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixclose2_portfolio_daily.xlsx
+++ b/output/quickfixclose2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>404,991.67</t>
+          <t>404,969.83</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+304.99%</t>
+          <t>+304.97%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,441  (13.6 pts of return)</t>
+          <t>5,463  (13.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5594,6 +5594,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>404991.67</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12028.66</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>392963.01</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 4,050); Nasdaq_100_E_mini short (risk 4,009); S_P_500_E_mini short (risk 3,969)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>404969.83</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>404969.83</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 3,930)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5606,7 +5662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10179,6 +10235,178 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>647900.0600000001</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>9005.809999999999</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>-31.27</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>647853.54</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>638894.25</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>8880.629999999999</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>647884.8100000001</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>630013.62</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>8757.190000000001</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>647851.6899999999</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>621256.4300000001</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>8635.459999999999</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>647885.3</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixclose2_portfolio_daily.xlsx
+++ b/output/quickfixclose2_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>404,969.83</t>
+          <t>403,102.83</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+304.97%</t>
+          <t>+303.10%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>418,568  (+318.57%)</t>
+          <t>416,702  (+316.70%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,463  (13.6 pts of return)</t>
+          <t>5,524  (13.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25.7x</t>
+          <t>25.5x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+4.26R  (best +21.10R)</t>
+          <t>+4.11R  (best +21.10R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,706  (+4.26%)</t>
+          <t>7,456  (+4.11%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,862  (-1.35%)</t>
+          <t>-1,881  (-1.31%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5627,26 +5627,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>404969.83</v>
+        <v>404991.67</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>15958.29</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>389033.38</v>
+      </c>
+      <c r="E190" t="n">
+        <v>4</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 3,930)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>403102.83</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>404969.83</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 3,930)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+      <c r="D191" s="5" t="n">
+        <v>403102.83</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 3,890); NY_Palladium_Futures short (risk 3,851)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-3,956); Nasdaq_100_E_mini exit_close (+1,284); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures exit_close (+1,378); S_P_500_E_mini exit_close (-568)</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10251,14 +10279,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="G90" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.003</v>
+        <v>0.34</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>647900.0600000001</v>
@@ -10266,15 +10302,15 @@
       <c r="J90" s="5" t="n">
         <v>9005.809999999999</v>
       </c>
-      <c r="K90" s="6" t="n">
-        <v>-31.27</v>
+      <c r="K90" s="7" t="n">
+        <v>3064.28</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>647853.54</v>
+        <v>645057.37</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10294,14 +10330,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-0</v>
+        <v>0.32</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>638894.25</v>
@@ -10309,15 +10353,15 @@
       <c r="J91" s="5" t="n">
         <v>8880.629999999999</v>
       </c>
-      <c r="K91" s="6" t="n">
-        <v>-0.49</v>
+      <c r="K91" s="7" t="n">
+        <v>2843.49</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>647884.8100000001</v>
+        <v>642049.04</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10337,14 +10381,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>-0.143</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-0</v>
+        <v>-0.143</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>630013.62</v>
@@ -10353,14 +10405,14 @@
         <v>8757.190000000001</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>-1.85</v>
+        <v>-1254.23</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>647851.6899999999</v>
+        <v>643803.14</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10380,14 +10432,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>621256.4300000001</v>
@@ -10396,12 +10456,98 @@
         <v>8635.459999999999</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>-14.76</v>
+        <v>-8694.51</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>647885.3</v>
+        <v>639205.55</v>
       </c>
       <c r="M93" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>612620.97</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>8515.43</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>-23.01</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>642026.02</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>604105.54</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>8397.07</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>-32.93</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>641993.09</v>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
